--- a/Hoàng/2025/T6/CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TPC (72-2025)/BÁO GIÁ KSK - CÔNG TY TNHH TM DV TPC.xlsx
+++ b/Hoàng/2025/T6/CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TPC (72-2025)/BÁO GIÁ KSK - CÔNG TY TNHH TM DV TPC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TPC (72-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0B1DBE-E350-4917-AC8D-ACF12A9F4AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EF7536-F41B-4A2A-BFBB-FF7B836D4254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -971,6 +971,90 @@
     <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -994,90 +1078,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1476,53 +1476,53 @@
       <c r="A1" s="19"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
-      <c r="D1" s="91" t="s">
+      <c r="D1" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="93"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="85"/>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21"/>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="93"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="85"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21"/>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="93"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="85"/>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21"/>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="85"/>
     </row>
     <row r="5" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="96"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="88"/>
     </row>
     <row r="6" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="20"/>
@@ -1535,16 +1535,16 @@
       <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="97" t="s">
+      <c r="A7" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="99"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="91"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -1568,31 +1568,31 @@
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="102"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="94"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="104"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="105"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="97"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -1600,14 +1600,14 @@
       <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
-      <c r="B11" s="107"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="108"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="100"/>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
@@ -1625,41 +1625,41 @@
       <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="117" t="s">
+      <c r="A13" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="117" t="s">
+      <c r="B13" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117" t="s">
+      <c r="C13" s="109"/>
+      <c r="D13" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="116" t="s">
+      <c r="E13" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="116" t="s">
+      <c r="F13" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="116"/>
-      <c r="H13" s="118" t="s">
+      <c r="G13" s="108"/>
+      <c r="H13" s="110" t="s">
         <v>0</v>
       </c>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:13" ht="33" x14ac:dyDescent="0.25">
-      <c r="A14" s="117"/>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="116"/>
+      <c r="A14" s="109"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="108"/>
       <c r="F14" s="68" t="s">
         <v>66</v>
       </c>
       <c r="G14" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="118"/>
+      <c r="H14" s="110"/>
       <c r="I14" s="76"/>
     </row>
     <row r="15" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1698,7 +1698,7 @@
       <c r="H16" s="35"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="66" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>2</v>
       </c>
@@ -1738,13 +1738,12 @@
         <v>82000</v>
       </c>
       <c r="G18" s="78">
-        <f t="shared" ref="G18" si="1">F18</f>
         <v>82000</v>
       </c>
       <c r="H18" s="35"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A19" s="32">
         <v>4</v>
       </c>
@@ -1760,7 +1759,6 @@
         <v>220000</v>
       </c>
       <c r="G19" s="78">
-        <f>F19</f>
         <v>220000</v>
       </c>
       <c r="H19" s="35"/>
@@ -1831,7 +1829,7 @@
       <c r="H22" s="35"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="32">
         <v>8</v>
       </c>
@@ -1849,7 +1847,6 @@
         <v>100000</v>
       </c>
       <c r="G23" s="78">
-        <f t="shared" ref="G23" si="2">F23</f>
         <v>100000</v>
       </c>
       <c r="H23" s="35"/>
@@ -1885,11 +1882,10 @@
         <v>27000</v>
       </c>
       <c r="F25" s="81">
-        <f t="shared" ref="F25:F26" si="3">ROUND(E25*80%,-3)</f>
+        <f t="shared" ref="F25:F26" si="1">ROUND(E25*80%,-3)</f>
         <v>22000</v>
       </c>
       <c r="G25" s="81">
-        <f t="shared" ref="G25:G26" si="4">F25</f>
         <v>22000</v>
       </c>
       <c r="H25" s="35"/>
@@ -1910,11 +1906,10 @@
         <v>47000</v>
       </c>
       <c r="F26" s="81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>38000</v>
       </c>
       <c r="G26" s="81">
-        <f t="shared" si="4"/>
         <v>38000</v>
       </c>
       <c r="H26" s="71"/>
@@ -1924,7 +1919,7 @@
       <c r="A27" s="32">
         <v>12</v>
       </c>
-      <c r="B27" s="109" t="s">
+      <c r="B27" s="101" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="36" t="s">
@@ -1933,35 +1928,35 @@
       <c r="D27" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="110">
+      <c r="E27" s="102">
         <v>60000</v>
       </c>
-      <c r="F27" s="114">
+      <c r="F27" s="106">
         <v>48000</v>
       </c>
-      <c r="G27" s="114">
+      <c r="G27" s="106">
         <v>48000</v>
       </c>
-      <c r="H27" s="112" t="s">
+      <c r="H27" s="104" t="s">
         <v>58</v>
       </c>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A28" s="32">
         <v>13</v>
       </c>
-      <c r="B28" s="109"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="36" t="s">
         <v>33</v>
       </c>
       <c r="D28" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="111"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="113"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="105"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" ht="66" x14ac:dyDescent="0.25">
@@ -1981,11 +1976,10 @@
         <v>75000</v>
       </c>
       <c r="F29" s="81">
-        <f t="shared" ref="F29" si="5">ROUND(E29*80%,-3)</f>
+        <f t="shared" ref="F29" si="2">ROUND(E29*80%,-3)</f>
         <v>60000</v>
       </c>
       <c r="G29" s="81">
-        <f t="shared" ref="G29" si="6">F29</f>
         <v>60000</v>
       </c>
       <c r="H29" s="35"/>
@@ -2008,17 +2002,16 @@
         <v>66000</v>
       </c>
       <c r="F30" s="81">
-        <f t="shared" ref="F30" si="7">ROUND(E30*80%,-3)</f>
+        <f t="shared" ref="F30" si="3">ROUND(E30*80%,-3)</f>
         <v>53000</v>
       </c>
       <c r="G30" s="81">
-        <f t="shared" ref="G30" si="8">F30</f>
         <v>53000</v>
       </c>
       <c r="H30" s="35"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32">
         <v>16</v>
       </c>
@@ -2039,7 +2032,6 @@
         <v>47000</v>
       </c>
       <c r="G31" s="81">
-        <f>F31</f>
         <v>47000</v>
       </c>
       <c r="H31" s="35"/>
@@ -2062,11 +2054,10 @@
         <v>41000</v>
       </c>
       <c r="F32" s="81">
-        <f t="shared" ref="F32:F33" si="9">ROUND(E32*80%,-3)</f>
+        <f t="shared" ref="F32:F33" si="4">ROUND(E32*80%,-3)</f>
         <v>33000</v>
       </c>
       <c r="G32" s="81">
-        <f t="shared" ref="G32:G33" si="10">F32</f>
         <v>33000</v>
       </c>
       <c r="H32" s="35"/>
@@ -2087,11 +2078,10 @@
         <v>41000</v>
       </c>
       <c r="F33" s="81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>33000</v>
       </c>
       <c r="G33" s="81">
-        <f t="shared" si="10"/>
         <v>33000</v>
       </c>
       <c r="H33" s="65" t="s">
@@ -2131,7 +2121,6 @@
         <v>139000</v>
       </c>
       <c r="G35" s="81">
-        <f>F35</f>
         <v>139000</v>
       </c>
       <c r="H35" s="35"/>
@@ -2152,17 +2141,16 @@
         <v>121000</v>
       </c>
       <c r="F36" s="81">
-        <f t="shared" ref="F36:F37" si="11">ROUND(E36*80%,-3)</f>
+        <f t="shared" ref="F36:F37" si="5">ROUND(E36*80%,-3)</f>
         <v>97000</v>
       </c>
       <c r="G36" s="81">
-        <f t="shared" ref="G36:G37" si="12">F36</f>
         <v>97000</v>
       </c>
       <c r="H36" s="35"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" s="13" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A37" s="32">
         <v>21</v>
       </c>
@@ -2177,23 +2165,22 @@
         <v>173000</v>
       </c>
       <c r="F37" s="81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>138000</v>
       </c>
       <c r="G37" s="81">
-        <f t="shared" si="12"/>
         <v>138000</v>
       </c>
       <c r="H37" s="35"/>
       <c r="I37" s="12"/>
     </row>
     <row r="38" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="83" t="s">
+      <c r="A38" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="84"/>
-      <c r="C38" s="84"/>
-      <c r="D38" s="85"/>
+      <c r="B38" s="112"/>
+      <c r="C38" s="112"/>
+      <c r="D38" s="113"/>
       <c r="E38" s="68">
         <f>SUM(E16:E37)</f>
         <v>2567000</v>
@@ -2231,12 +2218,12 @@
       <c r="H40" s="54"/>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="88" t="s">
+      <c r="A41" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="88"/>
-      <c r="C41" s="88"/>
-      <c r="D41" s="88"/>
+      <c r="B41" s="116"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="116"/>
       <c r="E41" s="23"/>
       <c r="F41" s="23"/>
       <c r="G41" s="23"/>
@@ -2244,63 +2231,63 @@
     </row>
     <row r="42" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="56"/>
-      <c r="B42" s="89" t="s">
+      <c r="B42" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="89"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="117"/>
     </row>
     <row r="43" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="56"/>
-      <c r="B43" s="89" t="s">
+      <c r="B43" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="89"/>
-      <c r="D43" s="89"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="89"/>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="117"/>
     </row>
     <row r="44" spans="1:9" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="57"/>
-      <c r="B44" s="89" t="s">
+      <c r="B44" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="89"/>
-      <c r="D44" s="89"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="89"/>
-      <c r="H44" s="89"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="117"/>
     </row>
     <row r="45" spans="1:9" s="14" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="58"/>
-      <c r="B45" s="90" t="s">
+      <c r="B45" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="90"/>
-      <c r="D45" s="90"/>
-      <c r="E45" s="90"/>
-      <c r="F45" s="90"/>
-      <c r="G45" s="90"/>
-      <c r="H45" s="90"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
+      <c r="H45" s="118"/>
     </row>
     <row r="46" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="55"/>
-      <c r="B46" s="89" t="s">
+      <c r="B46" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="89"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="117"/>
     </row>
     <row r="47" spans="1:9" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="55"/>
@@ -2340,10 +2327,10 @@
     </row>
     <row r="50" spans="1:8" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A50" s="55"/>
-      <c r="B50" s="86" t="s">
+      <c r="B50" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="C50" s="87"/>
+      <c r="C50" s="115"/>
       <c r="D50" s="59"/>
       <c r="E50" s="63"/>
       <c r="F50" s="63"/>
@@ -2376,6 +2363,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="D1:H5"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="B9:H9"/>
@@ -2391,14 +2386,6 @@
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="H13:H14"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
